--- a/artfynd/Holmtjärnen artfynd.xlsx
+++ b/artfynd/Holmtjärnen artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96972425</v>
+        <v>96972405</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680875</v>
+        <v>680720</v>
       </c>
       <c r="R2" t="n">
-        <v>7102579</v>
+        <v>7102804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112435885</v>
+        <v>96972430</v>
       </c>
       <c r="B3" t="n">
-        <v>92727</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,34 +791,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681590</v>
+        <v>680985</v>
       </c>
       <c r="R3" t="n">
-        <v>7102624</v>
+        <v>7102166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -845,12 +848,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -859,6 +862,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -881,45 +885,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112435868</v>
+        <v>96972433</v>
       </c>
       <c r="B4" t="n">
-        <v>92551</v>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681114</v>
+        <v>680970</v>
       </c>
       <c r="R4" t="n">
-        <v>7102142</v>
+        <v>7102176</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -946,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -960,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96972388</v>
+        <v>96972359</v>
       </c>
       <c r="B5" t="n">
-        <v>79569</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1020,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680910</v>
+        <v>680962</v>
       </c>
       <c r="R5" t="n">
-        <v>7102212</v>
+        <v>7102244</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,45 +1095,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112435859</v>
+        <v>96972382</v>
       </c>
       <c r="B6" t="n">
-        <v>90283</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681032</v>
+        <v>680942</v>
       </c>
       <c r="R6" t="n">
-        <v>7101956</v>
+        <v>7102250</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,12 +1163,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1166,6 +1177,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1188,45 +1200,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17225087</v>
+        <v>96972425</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mellan Holmtjärnen och Abborrtjärnen, vid nord-sydliga bäcken, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680969</v>
+        <v>680875</v>
       </c>
       <c r="R7" t="n">
-        <v>7102659</v>
+        <v>7102579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1253,12 +1268,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,36 +1282,19 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # sälg # Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1307,45 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112435884</v>
+        <v>112435861</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681468</v>
+        <v>680918</v>
       </c>
       <c r="R8" t="n">
-        <v>7102819</v>
+        <v>7102069</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1409,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112435861</v>
+        <v>96972410</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,34 +1417,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680918</v>
+        <v>680970</v>
       </c>
       <c r="R9" t="n">
-        <v>7102069</v>
+        <v>7102473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,6 +1488,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1510,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112435878</v>
+        <v>1999406</v>
       </c>
       <c r="B10" t="n">
-        <v>92551</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,34 +1522,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Mellan Holmtjärnen och Abborrtjärnen, vid nord-sydliga bäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>681482</v>
+        <v>680969</v>
       </c>
       <c r="R10" t="n">
-        <v>7102755</v>
+        <v>7102659</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,12 +1576,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,65 +1592,69 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112435876</v>
+        <v>96972367</v>
       </c>
       <c r="B11" t="n">
-        <v>92529</v>
+        <v>80467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>681448</v>
+        <v>680954</v>
       </c>
       <c r="R11" t="n">
-        <v>7102787</v>
+        <v>7102298</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1676,12 +1681,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1690,6 +1695,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1712,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112435870</v>
+        <v>96972419</v>
       </c>
       <c r="B12" t="n">
-        <v>78738</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1723,34 +1729,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>681215</v>
+        <v>680921</v>
       </c>
       <c r="R12" t="n">
-        <v>7101820</v>
+        <v>7102506</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,12 +1787,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>två individer</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1813,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96972382</v>
+        <v>96972388</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79917</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1824,21 +1839,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680942</v>
+        <v>680910</v>
       </c>
       <c r="R13" t="n">
-        <v>7102250</v>
+        <v>7102212</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112435887</v>
+        <v>96972394</v>
       </c>
       <c r="B14" t="n">
-        <v>92727</v>
+        <v>79917</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,34 +1944,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>681505</v>
+        <v>680742</v>
       </c>
       <c r="R14" t="n">
-        <v>7102856</v>
+        <v>7102795</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,12 +2001,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1997,6 +2015,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2019,48 +2038,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96972336</v>
+        <v>112435866</v>
       </c>
       <c r="B15" t="n">
-        <v>78647</v>
+        <v>92183</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>681148</v>
+        <v>681113</v>
       </c>
       <c r="R15" t="n">
-        <v>7102244</v>
+        <v>7101969</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,12 +2103,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2101,7 +2117,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2124,45 +2139,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112435871</v>
+        <v>112435859</v>
       </c>
       <c r="B16" t="n">
-        <v>90001</v>
+        <v>90932</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>681561</v>
+        <v>681032</v>
       </c>
       <c r="R16" t="n">
-        <v>7102667</v>
+        <v>7101956</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,11 +2243,11 @@
         <v>112435860</v>
       </c>
       <c r="B17" t="n">
-        <v>92551</v>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2326,48 +2341,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96972394</v>
+        <v>112435869</v>
       </c>
       <c r="B18" t="n">
-        <v>79569</v>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680742</v>
+        <v>681198</v>
       </c>
       <c r="R18" t="n">
-        <v>7102795</v>
+        <v>7101838</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,12 +2406,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2408,7 +2420,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2431,10 +2442,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112435863</v>
+        <v>112435867</v>
       </c>
       <c r="B19" t="n">
-        <v>91259</v>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2442,21 +2453,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2466,10 +2477,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>681051</v>
+        <v>681124</v>
       </c>
       <c r="R19" t="n">
-        <v>7102087</v>
+        <v>7101874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2532,10 +2543,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96972359</v>
+        <v>112436031</v>
       </c>
       <c r="B20" t="n">
-        <v>80084</v>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,37 +2554,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680962</v>
+        <v>681216</v>
       </c>
       <c r="R20" t="n">
-        <v>7102244</v>
+        <v>7101788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2600,12 +2608,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2614,7 +2622,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2637,32 +2644,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112435866</v>
+        <v>112435870</v>
       </c>
       <c r="B21" t="n">
-        <v>91506</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2672,10 +2679,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>681113</v>
+        <v>681215</v>
       </c>
       <c r="R21" t="n">
-        <v>7101969</v>
+        <v>7101820</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112435872</v>
+        <v>96972336</v>
       </c>
       <c r="B22" t="n">
-        <v>78980</v>
+        <v>78993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,34 +2756,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>681561</v>
+        <v>681148</v>
       </c>
       <c r="R22" t="n">
-        <v>7102797</v>
+        <v>7102244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2803,12 +2813,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2021-07-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,6 +2827,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2839,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112435869</v>
+        <v>112435864</v>
       </c>
       <c r="B23" t="n">
-        <v>92551</v>
+        <v>78993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2850,21 +2861,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2874,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>681198</v>
+        <v>681114</v>
       </c>
       <c r="R23" t="n">
-        <v>7101838</v>
+        <v>7102155</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2940,48 +2951,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96972410</v>
+        <v>112435863</v>
       </c>
       <c r="B24" t="n">
-        <v>79598</v>
+        <v>91923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680970</v>
+        <v>681051</v>
       </c>
       <c r="R24" t="n">
-        <v>7102473</v>
+        <v>7102087</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3008,12 +3016,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3022,7 +3030,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3045,10 +3052,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112435883</v>
+        <v>112435888</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>90932</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3056,21 +3063,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3080,13 +3087,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>681461</v>
+        <v>681524</v>
       </c>
       <c r="R25" t="n">
-        <v>7102844</v>
+        <v>7102855</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3146,14 +3153,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112435879</v>
+        <v>112435868</v>
       </c>
       <c r="B26" t="n">
-        <v>92551</v>
+        <v>93213</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3177,14 +3184,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>681445</v>
+        <v>681114</v>
       </c>
       <c r="R26" t="n">
-        <v>7102785</v>
+        <v>7102142</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,45 +3254,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112435865</v>
+        <v>112435873</v>
       </c>
       <c r="B27" t="n">
-        <v>5492</v>
+        <v>93213</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101410</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>681112</v>
+        <v>681535</v>
       </c>
       <c r="R27" t="n">
-        <v>7102060</v>
+        <v>7102684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3348,48 +3355,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96972430</v>
+        <v>112435878</v>
       </c>
       <c r="B28" t="n">
-        <v>78647</v>
+        <v>93213</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680985</v>
+        <v>681482</v>
       </c>
       <c r="R28" t="n">
-        <v>7102166</v>
+        <v>7102755</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,12 +3420,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3430,7 +3434,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3453,45 +3456,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1999407</v>
+        <v>112435879</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>93213</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mellan Holmtjärnen och Abborrtjärnen, vid nord-sydliga bäcken, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>681012</v>
+        <v>681445</v>
       </c>
       <c r="R29" t="n">
-        <v>7102578</v>
+        <v>7102785</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,12 +3521,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2012-10-11</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3534,69 +3537,65 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96972433</v>
+        <v>112435887</v>
       </c>
       <c r="B30" t="n">
-        <v>91406</v>
+        <v>91962</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680970</v>
+        <v>681505</v>
       </c>
       <c r="R30" t="n">
-        <v>7102176</v>
+        <v>7102856</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3623,12 +3622,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3637,7 +3636,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3660,10 +3658,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112435888</v>
+        <v>112435876</v>
       </c>
       <c r="B31" t="n">
-        <v>90283</v>
+        <v>93191</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3671,21 +3669,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3695,13 +3693,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>681524</v>
+        <v>681448</v>
       </c>
       <c r="R31" t="n">
-        <v>7102855</v>
+        <v>7102787</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3761,45 +3759,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112435867</v>
+        <v>112435871</v>
       </c>
       <c r="B32" t="n">
-        <v>92727</v>
+        <v>90691</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>6276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>681124</v>
+        <v>681561</v>
       </c>
       <c r="R32" t="n">
-        <v>7101874</v>
+        <v>7102667</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3862,45 +3860,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112435864</v>
+        <v>112435872</v>
       </c>
       <c r="B33" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>681114</v>
+        <v>681561</v>
       </c>
       <c r="R33" t="n">
-        <v>7102155</v>
+        <v>7102797</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3963,10 +3961,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96972419</v>
+        <v>112435862</v>
       </c>
       <c r="B34" t="n">
-        <v>57817</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3974,38 +3972,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680921</v>
+        <v>681039</v>
       </c>
       <c r="R34" t="n">
-        <v>7102506</v>
+        <v>7102079</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4032,17 +4026,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>två individer</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4073,10 +4062,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112435873</v>
+        <v>112435874</v>
       </c>
       <c r="B35" t="n">
-        <v>92551</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4084,21 +4073,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4108,10 +4097,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>681535</v>
+        <v>681499</v>
       </c>
       <c r="R35" t="n">
-        <v>7102684</v>
+        <v>7102758</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4174,10 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112436031</v>
+        <v>1999407</v>
       </c>
       <c r="B36" t="n">
-        <v>92529</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4185,34 +4174,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Mellan Holmtjärnen och Abborrtjärnen, vid nord-sydliga bäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>681216</v>
+        <v>681012</v>
       </c>
       <c r="R36" t="n">
-        <v>7101788</v>
+        <v>7102578</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4239,12 +4228,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4255,30 +4244,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112435862</v>
+        <v>112435883</v>
       </c>
       <c r="B37" t="n">
-        <v>79598</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4286,34 +4276,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Holmtjärnen, Ång</t>
+          <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>681039</v>
+        <v>681461</v>
       </c>
       <c r="R37" t="n">
-        <v>7102079</v>
+        <v>7102844</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4376,10 +4366,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112435874</v>
+        <v>112435884</v>
       </c>
       <c r="B38" t="n">
-        <v>79598</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4387,21 +4377,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4411,10 +4401,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>681499</v>
+        <v>681468</v>
       </c>
       <c r="R38" t="n">
-        <v>7102758</v>
+        <v>7102819</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,6 +4445,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4477,48 +4468,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96972367</v>
+        <v>112435865</v>
       </c>
       <c r="B39" t="n">
-        <v>80118</v>
+        <v>5495</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>101410</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långviskasjön, Ång</t>
+          <t>Holmtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680954</v>
+        <v>681112</v>
       </c>
       <c r="R39" t="n">
-        <v>7102298</v>
+        <v>7102060</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,12 +4533,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4559,7 +4547,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4582,10 +4569,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96972405</v>
+        <v>112435885</v>
       </c>
       <c r="B40" t="n">
-        <v>78647</v>
+        <v>91962</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4593,37 +4580,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långviskasjön, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680720</v>
+        <v>681590</v>
       </c>
       <c r="R40" t="n">
-        <v>7102804</v>
+        <v>7102624</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4650,12 +4634,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4664,7 +4648,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
